--- a/小野町_引継ぎ_整理済/22_図表管理/小野町_第10期計画_図表データ管理台帳_20261004.xlsx
+++ b/小野町_引継ぎ_整理済/22_図表管理/小野町_第10期計画_図表データ管理台帳_20261004.xlsx
@@ -7590,11 +7590,11 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>小野町高齢者保健福祉計画_第10期介護保険事業計画_素案_第7版_20260929.docx</t>
+          <t>小野町高齢者保健福祉計画_第10期介護保険事業計画_素案_第8版_20261004.docx</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>5</v>
@@ -7646,7 +7646,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>小野町_打合せ資料_現在地と論点_20260929.docx</t>
+          <t>小野町_打合せ資料_現在地と論点_20261004.docx</t>
         </is>
       </c>
       <c r="D7" s="6" t="n">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>小野町_打合せ次第_20260929.docx</t>
+          <t>小野町_打合せ次第_20261004.docx</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>小野町_打合せ記録_20260929.docx</t>
+          <t>小野町_打合せ記録_20261004.docx</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>小野町_計画素案_構成の対比と漏れの点検_20260929.docx</t>
+          <t>小野町_計画素案_構成の対比と漏れの点検_20261004.docx</t>
         </is>
       </c>
       <c r="D12" s="6" t="n">
@@ -7838,7 +7838,7 @@
       <c r="B14" s="6" t="inlineStr"/>
       <c r="C14" s="6" t="inlineStr"/>
       <c r="D14" s="6" t="n">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>26</v>
